--- a/data/modelling/atribucion/smartband/df_attr_alt_sent.xlsx
+++ b/data/modelling/atribucion/smartband/df_attr_alt_sent.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1370557884545111</v>
+        <v>0.2367883568122804</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6869924342977063</v>
+        <v>-0.6811749599053361</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2621154984291078</v>
+        <v>-0.1235922433636377</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.178256578086701</v>
+        <v>-1.269334633120778</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09796931038218969</v>
+        <v>0.1969002717606031</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.148557948547828</v>
+        <v>-1.130082724747607</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>0.655562937993766</v>
+        <v>0.8375103922951417</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2482879981584116</v>
+        <v>0.369598827722508</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8726427291092089</v>
+        <v>-0.9239983647985359</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.026384186636398</v>
+        <v>-1.094394991761368</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.435924116132501</v>
+        <v>-1.756263947352019</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6587116259883696</v>
+        <v>0.8411275207806362</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5500010635703246</v>
+        <v>-0.5475421223381367</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.32263754931939</v>
+        <v>-1.435211327335544</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.506671729884891</v>
+        <v>-1.642885284944136</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.068120227757817</v>
+        <v>-1.142800470803816</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7402727258033648</v>
+        <v>1.000915679386739</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7218422014645628</v>
+        <v>0.9313147238066961</v>
       </c>
     </row>
     <row r="20">
@@ -751,12 +751,12 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1.605597216726751</v>
+        <v>2.015291023129092</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18362373</v>
+        <v>17353248</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -764,15 +764,15 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.92080734565475</v>
+        <v>-1.007573577564792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17353248</v>
+        <v>15905518</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -783,12 +783,12 @@
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9504171286451689</v>
+        <v>-0.002662874483551936</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15905518</v>
+        <v>811935548</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -799,12 +799,12 @@
         <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1384506514522117</v>
+        <v>-1.840007061716951</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>811935548</v>
+        <v>18362367</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -812,15 +812,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.674975942668026</v>
+        <v>0.6948165072352377</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>18577715</v>
+        <v>18628975</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -828,15 +828,15 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02162442561441185</v>
+        <v>-0.776467233699035</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>18362367</v>
+        <v>16999363</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
         <v>21</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5313609942781047</v>
+        <v>0.8809148113159189</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18628975</v>
+        <v>17944054</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -860,15 +860,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7492597949294549</v>
+        <v>0.6682608124248171</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16999363</v>
+        <v>16649900</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -876,15 +876,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6933425747088221</v>
+        <v>-0.03725091918584777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>17944054</v>
+        <v>870551279</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -892,15 +892,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.5082465443112291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16649900</v>
+        <v>798823809</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -908,15 +906,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1024514834528578</v>
+        <v>0.9214326267697776</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>870551279</v>
+        <v>1129376761</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -924,13 +922,15 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.6064938262109361</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>18347134</v>
+        <v>925659331</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -938,15 +938,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>3.157311325889352</v>
+        <v>2.252844445068578</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>798823809</v>
+        <v>1130385828</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -954,15 +954,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.7286102124162168</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1129376761</v>
+        <v>18582027</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -970,15 +968,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5999638427905998</v>
+        <v>-0.4847852743439828</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>925659331</v>
+        <v>19146618</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -986,15 +984,15 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.88748445861375</v>
+        <v>0.06032690973056943</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1130385828</v>
+        <v>1114447581</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1002,13 +1000,15 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.4735944324138541</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18582027</v>
+        <v>15906639</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1016,15 +1016,15 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4935918384630848</v>
+        <v>1.405581166689101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>19146618</v>
+        <v>15974482</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1032,15 +1032,15 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.01716958973896072</v>
+        <v>0.7308629567923997</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1114447581</v>
+        <v>18554971</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1048,15 +1048,15 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4838111613812314</v>
+        <v>0.5077719177160276</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>15906639</v>
+        <v>899400867</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1064,15 +1064,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.150018121981038</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15974482</v>
+        <v>1113448743</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1083,12 +1081,12 @@
         <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3167342057948718</v>
+        <v>1.059914075539191</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>18554971</v>
+        <v>1130594835</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1096,15 +1094,15 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3685555438040393</v>
+        <v>-0.5525487084134244</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>899400867</v>
+        <v>931473181</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1112,13 +1110,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1113448743</v>
+        <v>809300742</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1126,15 +1124,15 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8564591027956808</v>
+        <v>-0.2883529257831816</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1130594835</v>
+        <v>912006408</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1142,15 +1140,15 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5528163217113432</v>
+        <v>1.544922845586657</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>931473181</v>
+        <v>1120397775</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1158,13 +1156,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>809300742</v>
+        <v>918271731</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1172,15 +1170,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.3219117897242066</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>912006408</v>
+        <v>1123066687</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1188,15 +1184,15 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>1.28035213550014</v>
+        <v>1.236025899305373</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1120397775</v>
+        <v>18728650</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1210,7 +1206,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>918271731</v>
+        <v>1117186349</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1224,7 +1220,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1123066687</v>
+        <v>1123490995</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1232,15 +1228,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>22</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1.002435047479997</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>18507562</v>
+        <v>1139787088</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1248,15 +1242,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.1096680040019594</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>18728650</v>
+        <v>18592587</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1264,13 +1256,15 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.425523041615658</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1117186349</v>
+        <v>19111235</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1278,13 +1272,15 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.1430065810834621</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1123490995</v>
+        <v>16656739</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1292,13 +1288,15 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.9392215021634158</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1139787088</v>
+        <v>761823849</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1306,13 +1304,15 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-1.062259918878131</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>18592587</v>
+        <v>1122496212</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1320,15 +1320,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.175997052572661</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19111235</v>
+        <v>903582249</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1336,15 +1334,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-0.1948803966254089</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>16656739</v>
+        <v>1116399707</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1352,15 +1348,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.8909229286868224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>761823849</v>
+        <v>1124466025</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1368,15 +1362,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>19</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.9980168975164658</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1122496212</v>
+        <v>905237295</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1384,13 +1376,15 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.02213373250803686</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>903582249</v>
+        <v>1117044965</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1404,7 +1398,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1116399707</v>
+        <v>1127626522</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1418,7 +1412,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1124466025</v>
+        <v>1125121096</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1432,7 +1426,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>905237295</v>
+        <v>822208885</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1440,15 +1434,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.0505501073201781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1117044965</v>
+        <v>929882638</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1462,7 +1454,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1127626522</v>
+        <v>886371185</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1476,7 +1468,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1125121096</v>
+        <v>1133985544</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1484,13 +1476,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>822208885</v>
+        <v>1112712822</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1504,7 +1496,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>929882638</v>
+        <v>925835044</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1518,7 +1510,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>886371185</v>
+        <v>932546799</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1532,7 +1524,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1133985544</v>
+        <v>877038180</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1540,13 +1532,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1112712822</v>
+        <v>918271785</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1560,7 +1552,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>925835044</v>
+        <v>848888616</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1568,13 +1560,15 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.9560346138989693</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>932546799</v>
+        <v>1122543689</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1588,7 +1582,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>877038180</v>
+        <v>1124107776</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1602,7 +1596,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>918271785</v>
+        <v>1136446808</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1616,7 +1610,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>848888616</v>
+        <v>692168723</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1627,12 +1621,12 @@
         <v>12</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7656694942490483</v>
+        <v>1.371075550971863</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1122543689</v>
+        <v>918660631</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1640,13 +1634,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1124467536</v>
+        <v>899860978</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1654,15 +1648,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
-      </c>
-      <c r="D80" t="n">
-        <v>2.240763378336481</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1124107776</v>
+        <v>935014675</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1676,7 +1668,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1136446808</v>
+        <v>1116357643</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1684,13 +1676,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>692168723</v>
+        <v>1113287659</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1698,15 +1690,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1.128411202234726</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>918660631</v>
+        <v>1127906765</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1714,13 +1704,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>899860978</v>
+        <v>884556384</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1728,13 +1718,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>935014675</v>
+        <v>1109687348</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1748,7 +1738,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1116357643</v>
+        <v>1135320848</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1756,13 +1746,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1113287659</v>
+        <v>1120667658</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -1776,7 +1766,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1127906765</v>
+        <v>930491860</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -1790,7 +1780,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>884556384</v>
+        <v>790644541</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -1798,13 +1788,15 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-0.5388825072960421</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1109687348</v>
+        <v>1106294913</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -1818,7 +1810,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1135320848</v>
+        <v>1127614056</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -1832,7 +1824,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1120667658</v>
+        <v>1121025951</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -1846,7 +1838,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>930491860</v>
+        <v>712525200</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -1854,13 +1846,15 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.2828637649558482</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>790644541</v>
+        <v>1132727262</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -1868,15 +1862,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-0.5408721572210383</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1106294913</v>
+        <v>1139080671</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -1890,7 +1882,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1127614056</v>
+        <v>1112931448</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -1904,7 +1896,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1121025951</v>
+        <v>1124096467</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -1918,7 +1910,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>712525200</v>
+        <v>1128039769</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -1926,15 +1918,15 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1727932439216184</v>
+        <v>-1.109929294743261</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1132727262</v>
+        <v>904381316</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -1942,13 +1934,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1139080671</v>
+        <v>1135493747</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -1962,7 +1954,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1112931448</v>
+        <v>1127578475</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -1976,7 +1968,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1124096467</v>
+        <v>1108103077</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -1984,13 +1976,15 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-0.1806429453858154</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1128039769</v>
+        <v>1102402604</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -1998,15 +1992,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-1.039961194416926</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>904381316</v>
+        <v>897968783</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -2014,13 +2006,15 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.02079342331122975</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1135493747</v>
+        <v>925402929</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2034,7 +2028,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1127578475</v>
+        <v>1124419501</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2048,7 +2042,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1108103077</v>
+        <v>925704016</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2056,15 +2050,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
-      </c>
-      <c r="D108" t="n">
-        <v>-0.2277745494717189</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1102402604</v>
+        <v>1122358418</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2072,13 +2064,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>897968783</v>
+        <v>1134504848</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2086,15 +2078,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>22</v>
-      </c>
-      <c r="D110" t="n">
-        <v>-0.0915130200260605</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>925402929</v>
+        <v>1127902407</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -2108,7 +2098,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1124419501</v>
+        <v>903963153</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2116,13 +2106,15 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-0.638998396669893</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>925704016</v>
+        <v>930314427</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -2136,7 +2128,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1122358418</v>
+        <v>1141242030</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -2144,13 +2136,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1134504848</v>
+        <v>1129804339</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -2164,7 +2156,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1127902407</v>
+        <v>1127740413</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -2178,7 +2170,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>920152079</v>
+        <v>932503270</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -2186,15 +2178,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>10</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0.7668907693086986</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>903963153</v>
+        <v>1140110031</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -2202,15 +2192,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>22</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-0.6296054391163848</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>930314427</v>
+        <v>1140039402</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -2224,7 +2212,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1141242030</v>
+        <v>1138045378</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -2238,7 +2226,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1129804339</v>
+        <v>1108117596</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -2252,7 +2240,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1127740413</v>
+        <v>1127728096</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -2266,7 +2254,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>932503270</v>
+        <v>1102095082</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -2280,7 +2268,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1140110031</v>
+        <v>906887097</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -2294,7 +2282,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1140039402</v>
+        <v>1102086547</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -2308,7 +2296,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1138045378</v>
+        <v>1121038437</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -2322,7 +2310,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1108117596</v>
+        <v>1129897442</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -2336,7 +2324,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1127728096</v>
+        <v>1120641152</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -2350,7 +2338,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1102095082</v>
+        <v>1104970649</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -2364,7 +2352,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>906887097</v>
+        <v>1137529813</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -2378,7 +2366,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1102086547</v>
+        <v>897929203</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -2392,7 +2380,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1121038437</v>
+        <v>931065158</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -2406,7 +2394,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1129897442</v>
+        <v>1138943749</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -2420,7 +2408,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1120641152</v>
+        <v>872253400</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -2434,7 +2422,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1104970649</v>
+        <v>1131163540</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -2448,7 +2436,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1137529813</v>
+        <v>1120444842</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -2462,7 +2450,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>897929203</v>
+        <v>1102096932</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -2476,7 +2464,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>931065158</v>
+        <v>1127833359</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -2490,7 +2478,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1138943749</v>
+        <v>878394448</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -2504,7 +2492,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>872253400</v>
+        <v>1137450477</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -2518,7 +2506,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1131163540</v>
+        <v>896351181</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -2532,605 +2520,603 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1120444842</v>
+        <v>1141999394</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1102096932</v>
+        <v>17796174</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-0.4807461887426318</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1127833359</v>
+        <v>15963018</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
-      </c>
-      <c r="D144" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.6754503147683657</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>878394448</v>
+        <v>16597584</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-0.5789508212931507</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1137450477</v>
+        <v>16219140</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
-      </c>
-      <c r="D146" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.6918383467735814</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>896351181</v>
+        <v>16140522</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>funciones</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-1.013913302602349</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1141999394</v>
+        <v>16930326</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.2106158095900849</v>
+        <v>-0.5525445819857899</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>17796174</v>
+        <v>18726729</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.1944500564839568</v>
+        <v>2.123263558070431</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>15963018</v>
+        <v>18533917</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.1371624858469231</v>
+        <v>-0.1037760013923603</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>16597584</v>
+        <v>16368723</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.2932364091342726</v>
+        <v>-1.911460406206544</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>16219140</v>
+        <v>16004823</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.468498482338261</v>
+        <v>-0.8632778552475777</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>16140522</v>
+        <v>17109416</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.05449707447398634</v>
+        <v>0.8244087299863849</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>16930326</v>
+        <v>18628977</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D154" t="n">
-        <v>1.100164689497385</v>
+        <v>-1.885185767089263</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>18726729</v>
+        <v>15983559</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D155" t="n">
-        <v>-2.338122529124011</v>
+        <v>1.255921539494656</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>18533917</v>
+        <v>16092653</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2897542685370604</v>
+        <v>0.883535245018602</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>16368723</v>
+        <v>18517515</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4986825176828642</v>
+        <v>0.9925295634549256</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>16004823</v>
+        <v>17232987</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>-2.109394081021633</v>
+        <v>-0.4128051141910248</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>17109416</v>
+        <v>796285393</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.2733611976320235</v>
+        <v>0.7807989801716455</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>18628977</v>
+        <v>16929984</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D160" t="n">
-        <v>-1.316941927696593</v>
+        <v>0.7447449985259005</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>15983559</v>
+        <v>17353248</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.2188123486885489</v>
+        <v>0.8893902612483736</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>16092653</v>
+        <v>15905518</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3403407180382139</v>
+        <v>0.5598904770419311</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>18517515</v>
+        <v>811935548</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>8</v>
       </c>
       <c r="D163" t="n">
-        <v>0.2430885344262825</v>
+        <v>-1.766865482126155</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>17232987</v>
+        <v>18362367</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D164" t="n">
-        <v>0.1902970287607795</v>
+        <v>-0.8622474709639321</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>796285393</v>
+        <v>18628975</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D165" t="n">
-        <v>1.651933581303093</v>
+        <v>-1.328377034126396</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>16929984</v>
+        <v>16999363</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.6146223416113471</v>
+        <v>-0.4231023770000882</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>18362373</v>
+        <v>17944054</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
-      </c>
-      <c r="D167" t="n">
-        <v>-0.3551916946720348</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>17353248</v>
+        <v>16649900</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>0.2043763412080158</v>
+        <v>1.278805538579265</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>15905518</v>
+        <v>870551279</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.8066631184256177</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>811935548</v>
+        <v>798823809</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D170" t="n">
-        <v>1.904432417314304</v>
+        <v>0.5456169694270226</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>18577715</v>
+        <v>1129376761</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-0.530471368121693</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>18362367</v>
+        <v>925659331</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
-        <v>0.05253316142355071</v>
+        <v>1.529391140383006</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>18628975</v>
+        <v>1130385828</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>9</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-1.006743154848778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>16999363</v>
+        <v>18582027</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>1.09860150543466</v>
+        <v>-0.4219163739719034</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>17944054</v>
+        <v>19146618</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-0.5953085032328198</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>16649900</v>
+        <v>1114447581</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0.835729636554307</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>870551279</v>
+        <v>15906639</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
-      </c>
-      <c r="D177" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1.057825633100849</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>18347134</v>
+        <v>15974482</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0.6015422698770966</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>798823809</v>
+        <v>18554971</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D179" t="n">
-        <v>1.187649822098335</v>
+        <v>0.5649961912388074</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1129376761</v>
+        <v>899400867</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3140,149 +3126,147 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>925659331</v>
+        <v>1113448743</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>1.308611065782801</v>
+        <v>0.9992088458135365</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1130385828</v>
+        <v>1130594835</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
-      </c>
-      <c r="D182" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-0.1312846690118292</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>18582027</v>
+        <v>931473181</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>4</v>
-      </c>
-      <c r="D183" t="n">
-        <v>-0.7346309580908353</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>19146618</v>
+        <v>809300742</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-0.4953682751862752</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1114447581</v>
+        <v>912006408</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.8392333122414196</v>
+        <v>-1.647425307033032</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>15906639</v>
+        <v>1120397775</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>4</v>
-      </c>
-      <c r="D186" t="n">
-        <v>1.235682832628386</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>15974482</v>
+        <v>918271731</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
-      </c>
-      <c r="D187" t="n">
-        <v>-1.281781408058849</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>18554971</v>
+        <v>1123066687</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>2.771104515540575</v>
+        <v>1.243142616420109</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>899400867</v>
+        <v>18728650</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1113448743</v>
+        <v>1117186349</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3292,133 +3276,129 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1130594835</v>
+        <v>1123490995</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>931473181</v>
+        <v>1139787088</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>5</v>
-      </c>
-      <c r="D192" t="n">
-        <v>1.968606879125587</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>809300742</v>
+        <v>18592587</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C193" t="n">
         <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2576868209653473</v>
+        <v>1.488337317901403</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>912006408</v>
+        <v>19111235</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>7</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-0.5829608600301099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1120397775</v>
+        <v>16656739</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-1.153791472567558</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>918271731</v>
+        <v>761823849</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
-      </c>
-      <c r="D196" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-1.317597879327663</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1123066687</v>
+        <v>1122496212</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>6</v>
-      </c>
-      <c r="D197" t="n">
-        <v>0.6721104573296071</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>18507562</v>
+        <v>903582249</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-0.2373360962869404</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>18728650</v>
+        <v>1116399707</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3428,11 +3408,11 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1117186349</v>
+        <v>1124466025</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3442,25 +3422,25 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1123490995</v>
+        <v>905237295</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1139787088</v>
+        <v>1117044965</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3470,27 +3450,25 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>18592587</v>
+        <v>1127626522</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
-      </c>
-      <c r="D203" t="n">
-        <v>-0.02736345816220492</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>19111235</v>
+        <v>1125121096</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3500,87 +3478,83 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>16656739</v>
+        <v>822208885</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>4</v>
-      </c>
-      <c r="D205" t="n">
-        <v>-0.580015779105969</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>761823849</v>
+        <v>929882638</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>21</v>
-      </c>
-      <c r="D206" t="n">
-        <v>0.5018922367747415</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1122496212</v>
+        <v>886371185</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>903582249</v>
+        <v>1133985544</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0</v>
-      </c>
-      <c r="D208" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.05867744138282412</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1116399707</v>
+        <v>1112712822</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1</v>
-      </c>
-      <c r="D209" t="n">
-        <v>-0.8819334105045912</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1124466025</v>
+        <v>925835044</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3590,43 +3564,39 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>905237295</v>
+        <v>932546799</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
-      </c>
-      <c r="D211" t="n">
-        <v>-0.213046434086205</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1117044965</v>
+        <v>877038180</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
-      </c>
-      <c r="D212" t="n">
-        <v>-1.629486672041879</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1127626522</v>
+        <v>918271785</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3636,41 +3606,41 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1125121096</v>
+        <v>848888616</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
-      </c>
-      <c r="D214" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-0.1429281081916882</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>822208885</v>
+        <v>1122543689</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
-      </c>
-      <c r="D215" t="n">
-        <v>-0.9173778604934871</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>929882638</v>
+        <v>1124107776</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3680,11 +3650,11 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>886371185</v>
+        <v>1136446808</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3694,57 +3664,57 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1133985544</v>
+        <v>692168723</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.4663528595467155</v>
+        <v>-1.245280630669687</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1112712822</v>
+        <v>918660631</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
-      </c>
-      <c r="D219" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-0.1623277990239695</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>925835044</v>
+        <v>899860978</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
-      </c>
-      <c r="D220" t="n">
-        <v>-0.2161502395616167</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>932546799</v>
+        <v>935014675</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3754,87 +3724,81 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>877038180</v>
+        <v>1116357643</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>918271785</v>
+        <v>1113287659</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1</v>
-      </c>
-      <c r="D223" t="n">
-        <v>-0.2578632255320795</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>848888616</v>
+        <v>1127906765</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
-      </c>
-      <c r="D224" t="n">
-        <v>-0.2009182551944836</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1122543689</v>
+        <v>884556384</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1124467536</v>
+        <v>1109687348</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2</v>
-      </c>
-      <c r="D226" t="n">
-        <v>-0.9219882992431007</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1124107776</v>
+        <v>1135320848</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3844,11 +3808,11 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1136446808</v>
+        <v>1120667658</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3858,43 +3822,41 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>692168723</v>
+        <v>930491860</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>7</v>
-      </c>
-      <c r="D229" t="n">
-        <v>1.251053498547315</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>918660631</v>
+        <v>790644541</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>4</v>
       </c>
       <c r="D230" t="n">
-        <v>-1.266933089463117</v>
+        <v>0.05388823441340669</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>899860978</v>
+        <v>1106294913</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3904,11 +3866,11 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>935014675</v>
+        <v>1127614056</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3918,41 +3880,41 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1116357643</v>
+        <v>1121025951</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
-      </c>
-      <c r="D233" t="n">
-        <v>0.4532727624798712</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1113287659</v>
+        <v>712525200</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0</v>
-      </c>
-      <c r="D234" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-0.2054755867282714</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1127906765</v>
+        <v>1132727262</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3962,27 +3924,25 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>884556384</v>
+        <v>1139080671</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>5</v>
-      </c>
-      <c r="D236" t="n">
-        <v>0.39092132863864</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1109687348</v>
+        <v>1112931448</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3992,11 +3952,11 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1135320848</v>
+        <v>1124096467</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4006,25 +3966,27 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1120667658</v>
+        <v>1128039769</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0</v>
-      </c>
-      <c r="D239" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.4023439177776867</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>930491860</v>
+        <v>904381316</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4034,27 +3996,25 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>790644541</v>
+        <v>1135493747</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
-      </c>
-      <c r="D241" t="n">
-        <v>-1.628479139583533</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1106294913</v>
+        <v>1127578475</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4064,25 +4024,27 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1127614056</v>
+        <v>1108103077</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>0</v>
-      </c>
-      <c r="D243" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="D243" t="n">
+        <v>-0.6594383766708896</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1121025951</v>
+        <v>1102402604</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4092,27 +4054,27 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>712525200</v>
+        <v>897968783</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D245" t="n">
-        <v>1.844776465141079</v>
+        <v>0.2911356963659985</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1132727262</v>
+        <v>925402929</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4122,11 +4084,11 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1139080671</v>
+        <v>1124419501</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4136,11 +4098,11 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1112931448</v>
+        <v>925704016</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4150,11 +4112,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1124096467</v>
+        <v>1122358418</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4164,57 +4126,55 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1128039769</v>
+        <v>1134504848</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>2</v>
-      </c>
-      <c r="D250" t="n">
-        <v>-0.1983884950964231</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>904381316</v>
+        <v>1127902407</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2</v>
-      </c>
-      <c r="D251" t="n">
-        <v>0.4842622552831375</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1135493747</v>
+        <v>903963153</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>0</v>
-      </c>
-      <c r="D252" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.6356331595466896</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1127578475</v>
+        <v>930314427</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4224,27 +4184,25 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1108103077</v>
+        <v>1141242030</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
-      </c>
-      <c r="D254" t="n">
-        <v>0.4818731335455017</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1102402604</v>
+        <v>1129804339</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4254,27 +4212,25 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>897968783</v>
+        <v>1127740413</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>8</v>
-      </c>
-      <c r="D256" t="n">
-        <v>1.483627979051643</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>925402929</v>
+        <v>932503270</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4284,11 +4240,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1124419501</v>
+        <v>1140110031</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4298,11 +4254,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>925704016</v>
+        <v>1140039402</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4312,27 +4268,25 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1122358418</v>
+        <v>1138045378</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1</v>
-      </c>
-      <c r="D260" t="n">
-        <v>-0.2144492189254515</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1134504848</v>
+        <v>1108117596</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4342,11 +4296,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1127902407</v>
+        <v>1127728096</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4356,43 +4310,39 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>920152079</v>
+        <v>1102095082</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1</v>
-      </c>
-      <c r="D263" t="n">
-        <v>-0.2109611252317281</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>903963153</v>
+        <v>906887097</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>5</v>
-      </c>
-      <c r="D264" t="n">
-        <v>-0.3708185384873935</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>930314427</v>
+        <v>1102086547</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4402,11 +4352,11 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1141242030</v>
+        <v>1121038437</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4416,11 +4366,11 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1129804339</v>
+        <v>1129897442</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4430,11 +4380,11 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1127740413</v>
+        <v>1120641152</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4444,11 +4394,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>932503270</v>
+        <v>1104970649</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4458,11 +4408,11 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1140110031</v>
+        <v>1137529813</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4472,11 +4422,11 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1140039402</v>
+        <v>897929203</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4486,11 +4436,11 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1138045378</v>
+        <v>931065158</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4500,11 +4450,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1108117596</v>
+        <v>1138943749</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4514,11 +4464,11 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1127728096</v>
+        <v>872253400</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4528,11 +4478,11 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1102095082</v>
+        <v>1131163540</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4542,11 +4492,11 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>906887097</v>
+        <v>1120444842</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4556,11 +4506,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1102086547</v>
+        <v>1102096932</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4570,11 +4520,11 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1121038437</v>
+        <v>1127833359</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4584,11 +4534,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1129897442</v>
+        <v>878394448</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4598,11 +4548,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1120641152</v>
+        <v>1137450477</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4612,2351 +4562,17 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1104970649</v>
+        <v>896351181</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>bluetooth</t>
         </is>
       </c>
       <c r="C281" t="n">
         <v>0</v>
       </c>
       <c r="D281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>1137529813</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>0</v>
-      </c>
-      <c r="D282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
-        <v>897929203</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>0</v>
-      </c>
-      <c r="D283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>931065158</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>0</v>
-      </c>
-      <c r="D284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
-        <v>1138943749</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C285" t="n">
-        <v>0</v>
-      </c>
-      <c r="D285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
-        <v>872253400</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C286" t="n">
-        <v>0</v>
-      </c>
-      <c r="D286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
-        <v>1131163540</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>0</v>
-      </c>
-      <c r="D287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
-        <v>1120444842</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>0</v>
-      </c>
-      <c r="D288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
-        <v>1102096932</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C289" t="n">
-        <v>0</v>
-      </c>
-      <c r="D289" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
-        <v>1127833359</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C290" t="n">
-        <v>0</v>
-      </c>
-      <c r="D290" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>878394448</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C291" t="n">
-        <v>0</v>
-      </c>
-      <c r="D291" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>1137450477</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>0</v>
-      </c>
-      <c r="D292" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>896351181</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>facil</t>
-        </is>
-      </c>
-      <c r="C293" t="n">
-        <v>0</v>
-      </c>
-      <c r="D293" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>1141999394</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>1</v>
-      </c>
-      <c r="D294" t="n">
-        <v>-0.6536458219237956</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>17796174</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C295" t="n">
-        <v>6</v>
-      </c>
-      <c r="D295" t="n">
-        <v>-0.5182136174742064</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>15963018</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>4</v>
-      </c>
-      <c r="D296" t="n">
-        <v>0.764233324035158</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>16597584</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>3</v>
-      </c>
-      <c r="D297" t="n">
-        <v>-0.7596952872975421</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
-        <v>16219140</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C298" t="n">
-        <v>10</v>
-      </c>
-      <c r="D298" t="n">
-        <v>0.6689028282138152</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>16140522</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C299" t="n">
-        <v>13</v>
-      </c>
-      <c r="D299" t="n">
-        <v>-0.8805389661092364</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>16930326</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C300" t="n">
-        <v>6</v>
-      </c>
-      <c r="D300" t="n">
-        <v>-0.5909015512236598</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
-        <v>18726729</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C301" t="n">
-        <v>6</v>
-      </c>
-      <c r="D301" t="n">
-        <v>2.497794578622678</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
-        <v>18533917</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C302" t="n">
-        <v>1</v>
-      </c>
-      <c r="D302" t="n">
-        <v>0.483214448142545</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
-        <v>16368723</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C303" t="n">
-        <v>5</v>
-      </c>
-      <c r="D303" t="n">
-        <v>-1.615683923659034</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
-        <v>16004823</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C304" t="n">
-        <v>10</v>
-      </c>
-      <c r="D304" t="n">
-        <v>-0.9426444272034811</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>17109416</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C305" t="n">
-        <v>7</v>
-      </c>
-      <c r="D305" t="n">
-        <v>0.8031163157764815</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
-        <v>18628977</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C306" t="n">
-        <v>9</v>
-      </c>
-      <c r="D306" t="n">
-        <v>-1.598157364114535</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
-        <v>15983559</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C307" t="n">
-        <v>4</v>
-      </c>
-      <c r="D307" t="n">
-        <v>1.272763800614298</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
-        <v>16092653</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C308" t="n">
-        <v>4</v>
-      </c>
-      <c r="D308" t="n">
-        <v>0.9989715317264832</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
-        <v>18517515</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C309" t="n">
-        <v>2</v>
-      </c>
-      <c r="D309" t="n">
-        <v>0.4712393617289253</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
-        <v>17232987</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C310" t="n">
-        <v>4</v>
-      </c>
-      <c r="D310" t="n">
-        <v>-0.3988029997603689</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="n">
-        <v>796285393</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C311" t="n">
-        <v>5</v>
-      </c>
-      <c r="D311" t="n">
-        <v>0.8852077159471525</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>16929984</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C312" t="n">
-        <v>11</v>
-      </c>
-      <c r="D312" t="n">
-        <v>0.6980928386422468</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
-        <v>18362373</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C313" t="n">
-        <v>3</v>
-      </c>
-      <c r="D313" t="n">
-        <v>-0.8226082391729417</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>17353248</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>3</v>
-      </c>
-      <c r="D314" t="n">
-        <v>1.009905284043747</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
-        <v>15905518</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C315" t="n">
-        <v>7</v>
-      </c>
-      <c r="D315" t="n">
-        <v>0.5237144761152464</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
-        <v>811935548</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C316" t="n">
-        <v>8</v>
-      </c>
-      <c r="D316" t="n">
-        <v>-1.820272100816247</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
-        <v>18577715</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C317" t="n">
-        <v>1</v>
-      </c>
-      <c r="D317" t="n">
-        <v>0.4713203731216114</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
-        <v>18362367</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C318" t="n">
-        <v>1</v>
-      </c>
-      <c r="D318" t="n">
-        <v>-0.8463106772329617</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>18628975</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C319" t="n">
-        <v>10</v>
-      </c>
-      <c r="D319" t="n">
-        <v>-0.932887346896897</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
-        <v>16999363</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C320" t="n">
-        <v>5</v>
-      </c>
-      <c r="D320" t="n">
-        <v>-1.139927461413832</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="n">
-        <v>17944054</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C321" t="n">
-        <v>1</v>
-      </c>
-      <c r="D321" t="n">
-        <v>-0.17628602876076</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
-        <v>16649900</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C322" t="n">
-        <v>6</v>
-      </c>
-      <c r="D322" t="n">
-        <v>1.50287827980441</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>870551279</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C323" t="n">
-        <v>0</v>
-      </c>
-      <c r="D323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
-        <v>18347134</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C324" t="n">
-        <v>1</v>
-      </c>
-      <c r="D324" t="n">
-        <v>0.4828176733544167</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>798823809</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C325" t="n">
-        <v>8</v>
-      </c>
-      <c r="D325" t="n">
-        <v>0.5208699909063078</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="n">
-        <v>1129376761</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C326" t="n">
-        <v>0</v>
-      </c>
-      <c r="D326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>925659331</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>4</v>
-      </c>
-      <c r="D327" t="n">
-        <v>1.744834298174142</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="n">
-        <v>1130385828</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C328" t="n">
-        <v>0</v>
-      </c>
-      <c r="D328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>18582027</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C329" t="n">
-        <v>3</v>
-      </c>
-      <c r="D329" t="n">
-        <v>-0.4959002070440722</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="n">
-        <v>19146618</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C330" t="n">
-        <v>0</v>
-      </c>
-      <c r="D330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>1114447581</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>1</v>
-      </c>
-      <c r="D331" t="n">
-        <v>-0.05950202245729924</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>15906639</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>8</v>
-      </c>
-      <c r="D332" t="n">
-        <v>1.039425841495868</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>15974482</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C333" t="n">
-        <v>0</v>
-      </c>
-      <c r="D333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
-        <v>18554971</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C334" t="n">
-        <v>3</v>
-      </c>
-      <c r="D334" t="n">
-        <v>0.7634125207451646</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>899400867</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>0</v>
-      </c>
-      <c r="D335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
-        <v>1113448743</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C336" t="n">
-        <v>3</v>
-      </c>
-      <c r="D336" t="n">
-        <v>1.136013157065855</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>1130594835</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C337" t="n">
-        <v>2</v>
-      </c>
-      <c r="D337" t="n">
-        <v>-0.1621606657953597</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="n">
-        <v>931473181</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C338" t="n">
-        <v>0</v>
-      </c>
-      <c r="D338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>809300742</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>4</v>
-      </c>
-      <c r="D339" t="n">
-        <v>-0.1509642845273599</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
-        <v>912006408</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>17</v>
-      </c>
-      <c r="D340" t="n">
-        <v>-1.699351624102386</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>1120397775</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>0</v>
-      </c>
-      <c r="D341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
-        <v>918271731</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>0</v>
-      </c>
-      <c r="D342" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
-        <v>1123066687</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>8</v>
-      </c>
-      <c r="D343" t="n">
-        <v>1.407935470188423</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
-        <v>18507562</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>0</v>
-      </c>
-      <c r="D344" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
-        <v>18728650</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>1</v>
-      </c>
-      <c r="D345" t="n">
-        <v>-0.8306461133555129</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
-        <v>1117186349</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C346" t="n">
-        <v>0</v>
-      </c>
-      <c r="D346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
-        <v>1123490995</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>1</v>
-      </c>
-      <c r="D347" t="n">
-        <v>-0.8433214564068381</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="n">
-        <v>1139787088</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>0</v>
-      </c>
-      <c r="D348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>18592587</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>3</v>
-      </c>
-      <c r="D349" t="n">
-        <v>1.697691583545185</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="n">
-        <v>19111235</v>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>0</v>
-      </c>
-      <c r="D350" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>16656739</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>10</v>
-      </c>
-      <c r="D351" t="n">
-        <v>-1.503081164869973</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="n">
-        <v>761823849</v>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>14</v>
-      </c>
-      <c r="D352" t="n">
-        <v>-1.365436249581169</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>1122496212</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>0</v>
-      </c>
-      <c r="D353" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
-        <v>903582249</v>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>0</v>
-      </c>
-      <c r="D354" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
-        <v>1116399707</v>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>0</v>
-      </c>
-      <c r="D355" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
-        <v>1124466025</v>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>0</v>
-      </c>
-      <c r="D356" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
-        <v>905237295</v>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>1</v>
-      </c>
-      <c r="D357" t="n">
-        <v>-0.8428127585659257</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
-        <v>1117044965</v>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>0</v>
-      </c>
-      <c r="D358" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
-        <v>1127626522</v>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>0</v>
-      </c>
-      <c r="D359" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
-        <v>1125121096</v>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>0</v>
-      </c>
-      <c r="D360" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
-        <v>822208885</v>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>0</v>
-      </c>
-      <c r="D361" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
-        <v>929882638</v>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>0</v>
-      </c>
-      <c r="D362" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
-        <v>886371185</v>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>1</v>
-      </c>
-      <c r="D363" t="n">
-        <v>-0.1796274882101299</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
-        <v>1133985544</v>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>2</v>
-      </c>
-      <c r="D364" t="n">
-        <v>0.05597712373698763</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
-        <v>1112712822</v>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>0</v>
-      </c>
-      <c r="D365" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
-        <v>925835044</v>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>0</v>
-      </c>
-      <c r="D366" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
-        <v>932546799</v>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>0</v>
-      </c>
-      <c r="D367" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
-        <v>877038180</v>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C368" t="n">
-        <v>0</v>
-      </c>
-      <c r="D368" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
-        <v>918271785</v>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C369" t="n">
-        <v>0</v>
-      </c>
-      <c r="D369" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" t="n">
-        <v>848888616</v>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C370" t="n">
-        <v>2</v>
-      </c>
-      <c r="D370" t="n">
-        <v>-0.1755311160516556</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>1122543689</v>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C371" t="n">
-        <v>0</v>
-      </c>
-      <c r="D371" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>1124467536</v>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C372" t="n">
-        <v>3</v>
-      </c>
-      <c r="D372" t="n">
-        <v>1.72273194558349</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
-        <v>1124107776</v>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>0</v>
-      </c>
-      <c r="D373" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>1136446808</v>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C374" t="n">
-        <v>0</v>
-      </c>
-      <c r="D374" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" t="n">
-        <v>692168723</v>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C375" t="n">
-        <v>5</v>
-      </c>
-      <c r="D375" t="n">
-        <v>-1.34379517085421</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>918660631</v>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C376" t="n">
-        <v>2</v>
-      </c>
-      <c r="D376" t="n">
-        <v>-0.1978082636887394</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
-        <v>899860978</v>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C377" t="n">
-        <v>0</v>
-      </c>
-      <c r="D377" t="inlineStr"/>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
-        <v>935014675</v>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C378" t="n">
-        <v>0</v>
-      </c>
-      <c r="D378" t="inlineStr"/>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
-        <v>1116357643</v>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>0</v>
-      </c>
-      <c r="D379" t="inlineStr"/>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
-        <v>1113287659</v>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>0</v>
-      </c>
-      <c r="D380" t="inlineStr"/>
-    </row>
-    <row r="381">
-      <c r="A381" t="n">
-        <v>1127906765</v>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C381" t="n">
-        <v>0</v>
-      </c>
-      <c r="D381" t="inlineStr"/>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>884556384</v>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>1</v>
-      </c>
-      <c r="D382" t="n">
-        <v>0.4801376420212185</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>1109687348</v>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>0</v>
-      </c>
-      <c r="D383" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>1135320848</v>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C384" t="n">
-        <v>0</v>
-      </c>
-      <c r="D384" t="inlineStr"/>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>1120667658</v>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C385" t="n">
-        <v>0</v>
-      </c>
-      <c r="D385" t="inlineStr"/>
-    </row>
-    <row r="386">
-      <c r="A386" t="n">
-        <v>930491860</v>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C386" t="n">
-        <v>0</v>
-      </c>
-      <c r="D386" t="inlineStr"/>
-    </row>
-    <row r="387">
-      <c r="A387" t="n">
-        <v>790644541</v>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C387" t="n">
-        <v>4</v>
-      </c>
-      <c r="D387" t="n">
-        <v>0.05047759136838249</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="n">
-        <v>1106294913</v>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C388" t="n">
-        <v>0</v>
-      </c>
-      <c r="D388" t="inlineStr"/>
-    </row>
-    <row r="389">
-      <c r="A389" t="n">
-        <v>1127614056</v>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C389" t="n">
-        <v>0</v>
-      </c>
-      <c r="D389" t="inlineStr"/>
-    </row>
-    <row r="390">
-      <c r="A390" t="n">
-        <v>1121025951</v>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C390" t="n">
-        <v>0</v>
-      </c>
-      <c r="D390" t="inlineStr"/>
-    </row>
-    <row r="391">
-      <c r="A391" t="n">
-        <v>712525200</v>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C391" t="n">
-        <v>5</v>
-      </c>
-      <c r="D391" t="n">
-        <v>-0.7253145939713947</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="n">
-        <v>1132727262</v>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C392" t="n">
-        <v>0</v>
-      </c>
-      <c r="D392" t="inlineStr"/>
-    </row>
-    <row r="393">
-      <c r="A393" t="n">
-        <v>1139080671</v>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C393" t="n">
-        <v>0</v>
-      </c>
-      <c r="D393" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" t="n">
-        <v>1112931448</v>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C394" t="n">
-        <v>0</v>
-      </c>
-      <c r="D394" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" t="n">
-        <v>1124096467</v>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C395" t="n">
-        <v>0</v>
-      </c>
-      <c r="D395" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" t="n">
-        <v>1128039769</v>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C396" t="n">
-        <v>3</v>
-      </c>
-      <c r="D396" t="n">
-        <v>-0.4734249036074342</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="n">
-        <v>904381316</v>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C397" t="n">
-        <v>0</v>
-      </c>
-      <c r="D397" t="inlineStr"/>
-    </row>
-    <row r="398">
-      <c r="A398" t="n">
-        <v>1135493747</v>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C398" t="n">
-        <v>0</v>
-      </c>
-      <c r="D398" t="inlineStr"/>
-    </row>
-    <row r="399">
-      <c r="A399" t="n">
-        <v>1127578475</v>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C399" t="n">
-        <v>0</v>
-      </c>
-      <c r="D399" t="inlineStr"/>
-    </row>
-    <row r="400">
-      <c r="A400" t="n">
-        <v>1108103077</v>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C400" t="n">
-        <v>3</v>
-      </c>
-      <c r="D400" t="n">
-        <v>-0.7686527070615085</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="n">
-        <v>1102402604</v>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C401" t="n">
-        <v>0</v>
-      </c>
-      <c r="D401" t="inlineStr"/>
-    </row>
-    <row r="402">
-      <c r="A402" t="n">
-        <v>897968783</v>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C402" t="n">
-        <v>6</v>
-      </c>
-      <c r="D402" t="n">
-        <v>0.8996766229131115</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="n">
-        <v>925402929</v>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C403" t="n">
-        <v>0</v>
-      </c>
-      <c r="D403" t="inlineStr"/>
-    </row>
-    <row r="404">
-      <c r="A404" t="n">
-        <v>1124419501</v>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C404" t="n">
-        <v>0</v>
-      </c>
-      <c r="D404" t="inlineStr"/>
-    </row>
-    <row r="405">
-      <c r="A405" t="n">
-        <v>925704016</v>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C405" t="n">
-        <v>0</v>
-      </c>
-      <c r="D405" t="inlineStr"/>
-    </row>
-    <row r="406">
-      <c r="A406" t="n">
-        <v>1122358418</v>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C406" t="n">
-        <v>0</v>
-      </c>
-      <c r="D406" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" t="n">
-        <v>1134504848</v>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C407" t="n">
-        <v>0</v>
-      </c>
-      <c r="D407" t="inlineStr"/>
-    </row>
-    <row r="408">
-      <c r="A408" t="n">
-        <v>1127902407</v>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C408" t="n">
-        <v>0</v>
-      </c>
-      <c r="D408" t="inlineStr"/>
-    </row>
-    <row r="409">
-      <c r="A409" t="n">
-        <v>920152079</v>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C409" t="n">
-        <v>2</v>
-      </c>
-      <c r="D409" t="n">
-        <v>-0.1514512021377591</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="n">
-        <v>903963153</v>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C410" t="n">
-        <v>8</v>
-      </c>
-      <c r="D410" t="n">
-        <v>0.6120011877148754</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="n">
-        <v>930314427</v>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C411" t="n">
-        <v>0</v>
-      </c>
-      <c r="D411" t="inlineStr"/>
-    </row>
-    <row r="412">
-      <c r="A412" t="n">
-        <v>1141242030</v>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C412" t="n">
-        <v>0</v>
-      </c>
-      <c r="D412" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" t="n">
-        <v>1129804339</v>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C413" t="n">
-        <v>0</v>
-      </c>
-      <c r="D413" t="inlineStr"/>
-    </row>
-    <row r="414">
-      <c r="A414" t="n">
-        <v>1127740413</v>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C414" t="n">
-        <v>0</v>
-      </c>
-      <c r="D414" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" t="n">
-        <v>932503270</v>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C415" t="n">
-        <v>0</v>
-      </c>
-      <c r="D415" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" t="n">
-        <v>1140110031</v>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C416" t="n">
-        <v>0</v>
-      </c>
-      <c r="D416" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" t="n">
-        <v>1140039402</v>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C417" t="n">
-        <v>0</v>
-      </c>
-      <c r="D417" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" t="n">
-        <v>1138045378</v>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C418" t="n">
-        <v>0</v>
-      </c>
-      <c r="D418" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" t="n">
-        <v>1108117596</v>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C419" t="n">
-        <v>0</v>
-      </c>
-      <c r="D419" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" t="n">
-        <v>1127728096</v>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C420" t="n">
-        <v>0</v>
-      </c>
-      <c r="D420" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" t="n">
-        <v>1102095082</v>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C421" t="n">
-        <v>0</v>
-      </c>
-      <c r="D421" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" t="n">
-        <v>906887097</v>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C422" t="n">
-        <v>0</v>
-      </c>
-      <c r="D422" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" t="n">
-        <v>1102086547</v>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C423" t="n">
-        <v>0</v>
-      </c>
-      <c r="D423" t="inlineStr"/>
-    </row>
-    <row r="424">
-      <c r="A424" t="n">
-        <v>1121038437</v>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C424" t="n">
-        <v>0</v>
-      </c>
-      <c r="D424" t="inlineStr"/>
-    </row>
-    <row r="425">
-      <c r="A425" t="n">
-        <v>1129897442</v>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C425" t="n">
-        <v>0</v>
-      </c>
-      <c r="D425" t="inlineStr"/>
-    </row>
-    <row r="426">
-      <c r="A426" t="n">
-        <v>1120641152</v>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C426" t="n">
-        <v>0</v>
-      </c>
-      <c r="D426" t="inlineStr"/>
-    </row>
-    <row r="427">
-      <c r="A427" t="n">
-        <v>1104970649</v>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C427" t="n">
-        <v>0</v>
-      </c>
-      <c r="D427" t="inlineStr"/>
-    </row>
-    <row r="428">
-      <c r="A428" t="n">
-        <v>1137529813</v>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C428" t="n">
-        <v>0</v>
-      </c>
-      <c r="D428" t="inlineStr"/>
-    </row>
-    <row r="429">
-      <c r="A429" t="n">
-        <v>897929203</v>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C429" t="n">
-        <v>0</v>
-      </c>
-      <c r="D429" t="inlineStr"/>
-    </row>
-    <row r="430">
-      <c r="A430" t="n">
-        <v>931065158</v>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C430" t="n">
-        <v>0</v>
-      </c>
-      <c r="D430" t="inlineStr"/>
-    </row>
-    <row r="431">
-      <c r="A431" t="n">
-        <v>1138943749</v>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C431" t="n">
-        <v>0</v>
-      </c>
-      <c r="D431" t="inlineStr"/>
-    </row>
-    <row r="432">
-      <c r="A432" t="n">
-        <v>872253400</v>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C432" t="n">
-        <v>0</v>
-      </c>
-      <c r="D432" t="inlineStr"/>
-    </row>
-    <row r="433">
-      <c r="A433" t="n">
-        <v>1131163540</v>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C433" t="n">
-        <v>0</v>
-      </c>
-      <c r="D433" t="inlineStr"/>
-    </row>
-    <row r="434">
-      <c r="A434" t="n">
-        <v>1120444842</v>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C434" t="n">
-        <v>0</v>
-      </c>
-      <c r="D434" t="inlineStr"/>
-    </row>
-    <row r="435">
-      <c r="A435" t="n">
-        <v>1102096932</v>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C435" t="n">
-        <v>0</v>
-      </c>
-      <c r="D435" t="inlineStr"/>
-    </row>
-    <row r="436">
-      <c r="A436" t="n">
-        <v>1127833359</v>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C436" t="n">
-        <v>0</v>
-      </c>
-      <c r="D436" t="inlineStr"/>
-    </row>
-    <row r="437">
-      <c r="A437" t="n">
-        <v>878394448</v>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C437" t="n">
-        <v>0</v>
-      </c>
-      <c r="D437" t="inlineStr"/>
-    </row>
-    <row r="438">
-      <c r="A438" t="n">
-        <v>1137450477</v>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C438" t="n">
-        <v>0</v>
-      </c>
-      <c r="D438" t="inlineStr"/>
-    </row>
-    <row r="439">
-      <c r="A439" t="n">
-        <v>896351181</v>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>conecta</t>
-        </is>
-      </c>
-      <c r="C439" t="n">
-        <v>0</v>
-      </c>
-      <c r="D439" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
